--- a/artfynd/A 56172-2022 artfynd.xlsx
+++ b/artfynd/A 56172-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56172-2022 artfynd.xlsx
+++ b/artfynd/A 56172-2022 artfynd.xlsx
@@ -2806,7 +2806,7 @@
         <v>119714556</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 56172-2022 artfynd.xlsx
+++ b/artfynd/A 56172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91820391</v>
+        <v>91820389</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792447.929428296</v>
+        <v>792365</v>
       </c>
       <c r="R2" t="n">
-        <v>7354525.833729008</v>
+        <v>7354475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91820347</v>
+        <v>91820369</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792501.2096894301</v>
+        <v>792412</v>
       </c>
       <c r="R3" t="n">
-        <v>7354565.988424786</v>
+        <v>7354529</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91820325</v>
+        <v>91820385</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792453.9552827136</v>
+        <v>792368</v>
       </c>
       <c r="R4" t="n">
-        <v>7354651.845769764</v>
+        <v>7354386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91820354</v>
+        <v>91820374</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792558.2461457669</v>
+        <v>792384</v>
       </c>
       <c r="R5" t="n">
-        <v>7354663.934873462</v>
+        <v>7354578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,19 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91820377</v>
+        <v>91820376</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792384.9250397275</v>
+        <v>792389</v>
       </c>
       <c r="R6" t="n">
-        <v>7354586.848309446</v>
+        <v>7354565</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91820374</v>
+        <v>91820377</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>792384.1932845772</v>
+        <v>792385</v>
       </c>
       <c r="R7" t="n">
-        <v>7354578.223190884</v>
+        <v>7354587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91820321</v>
+        <v>91820383</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>792498.060890534</v>
+        <v>792405</v>
       </c>
       <c r="R8" t="n">
-        <v>7354686.158366068</v>
+        <v>7354545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91820352</v>
+        <v>91820373</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>792451.0675179539</v>
+        <v>792412</v>
       </c>
       <c r="R9" t="n">
-        <v>7354667.828167814</v>
+        <v>7354529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91820382</v>
+        <v>91820379</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>792439.9662732746</v>
+        <v>792408</v>
       </c>
       <c r="R10" t="n">
-        <v>7354520.118926036</v>
+        <v>7354545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91820367</v>
+        <v>91820382</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>792462.0294626241</v>
+        <v>792440</v>
       </c>
       <c r="R11" t="n">
-        <v>7354500.026836612</v>
+        <v>7354520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91820383</v>
+        <v>91820391</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>792405.1790341048</v>
+        <v>792448</v>
       </c>
       <c r="R12" t="n">
-        <v>7354544.991983407</v>
+        <v>7354526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91820369</v>
+        <v>91820321</v>
       </c>
       <c r="B13" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>792412.1402423121</v>
+        <v>792498</v>
       </c>
       <c r="R13" t="n">
-        <v>7354529.026110045</v>
+        <v>7354686</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91820376</v>
+        <v>91820325</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>792389.2480045473</v>
+        <v>792454</v>
       </c>
       <c r="R14" t="n">
-        <v>7354564.908565938</v>
+        <v>7354652</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91820375</v>
+        <v>91820329</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>792410.1176997828</v>
+        <v>792531</v>
       </c>
       <c r="R15" t="n">
-        <v>7354470.192600592</v>
+        <v>7354717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>91820384</v>
+        <v>91820347</v>
       </c>
       <c r="B16" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>792390.8908887682</v>
+        <v>792501</v>
       </c>
       <c r="R16" t="n">
-        <v>7354466.968592108</v>
+        <v>7354566</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>91820389</v>
+        <v>91820352</v>
       </c>
       <c r="B17" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>792365.2063016864</v>
+        <v>792451</v>
       </c>
       <c r="R17" t="n">
-        <v>7354474.878212009</v>
+        <v>7354668</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>91820373</v>
+        <v>91820353</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>792412.1402423121</v>
+        <v>792460</v>
       </c>
       <c r="R18" t="n">
-        <v>7354529.026110045</v>
+        <v>7354683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>91820379</v>
+        <v>91820367</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>792408.043171017</v>
+        <v>792462</v>
       </c>
       <c r="R19" t="n">
-        <v>7354544.883234783</v>
+        <v>7354500</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2392,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>91820353</v>
+        <v>91820375</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>792460.0809055812</v>
+        <v>792410</v>
       </c>
       <c r="R20" t="n">
-        <v>7354683.015059006</v>
+        <v>7354470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2489,9 @@
           <t>2020-08-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,50 +2518,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119714556</v>
+        <v>91820380</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Åbojen, Nb</t>
+          <t>Åbojen utvidgning, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>792419</v>
+        <v>792338</v>
       </c>
       <c r="R21" t="n">
-        <v>7354475</v>
+        <v>7354422</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-08-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,19 +2603,516 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119714577</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Åbojen, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>792417</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7354468</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119782246</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Åbojen, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>792433</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7354429</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119714556</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Åbojen, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>792419</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7354475</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>119782290</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Åbojen, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>792433</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7354429</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>91820384</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Åbojen utvidgning, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>792391</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7354467</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-08-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56172-2022 artfynd.xlsx
+++ b/artfynd/A 56172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820389</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820385</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820383</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820373</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820379</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820382</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820391</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820321</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820325</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820329</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820347</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820352</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820353</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820367</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820375</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820380</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2713,6 +2818,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119714577</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119782246</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119714556</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3016,6 +3136,11 @@
           <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119782290</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3113,8 +3238,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91820384</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>